--- a/annotation_categories/spanish/dataset_ES_csv_categories.xlsx
+++ b/annotation_categories/spanish/dataset_ES_csv_categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFM\b_Dataset\Dataset\Final_Datasets_tobesent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFFCFD2-A38F-4196-9F16-F42A145227C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7047CAFE-A577-47EC-8F03-259084ED4310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="190" windowWidth="19200" windowHeight="11090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -9396,9 +9396,6 @@
     <t>2.2</t>
   </si>
   <si>
-    <t>macrocategory</t>
-  </si>
-  <si>
     <t>subcategory</t>
   </si>
   <si>
@@ -9454,6 +9451,9 @@
   </si>
   <si>
     <t>Hyperbole and exaggeration</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
 </sst>
 </file>
@@ -9712,7 +9712,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -9814,20 +9814,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12879,13 +12873,13 @@
         <v>680</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>915</v>
+        <v>934</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>904</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F1" s="25" t="s">
         <v>172</v>
@@ -12903,13 +12897,13 @@
         <v>705</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>281</v>
@@ -12927,13 +12921,13 @@
         <v>713</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>296</v>
@@ -12951,13 +12945,13 @@
         <v>733</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>332</v>
@@ -12975,13 +12969,13 @@
         <v>749</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F5" s="21" t="s">
         <v>360</v>
@@ -12999,13 +12993,13 @@
         <v>750</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D6" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>361</v>
@@ -13023,13 +13017,13 @@
         <v>752</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>364</v>
@@ -13047,13 +13041,13 @@
         <v>779</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>417</v>
@@ -13071,13 +13065,13 @@
         <v>783</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>689</v>
@@ -13095,13 +13089,13 @@
         <v>784</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>424</v>
@@ -13119,13 +13113,13 @@
         <v>787</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>428</v>
@@ -13143,13 +13137,13 @@
         <v>789</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D12" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>431</v>
@@ -13167,13 +13161,13 @@
         <v>790</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>245</v>
@@ -13191,13 +13185,13 @@
         <v>792</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D14" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>437</v>
@@ -13215,13 +13209,13 @@
         <v>803</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>454</v>
@@ -13239,13 +13233,13 @@
         <v>806</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D16" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>694</v>
@@ -13263,13 +13257,13 @@
         <v>807</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>469</v>
@@ -13287,13 +13281,13 @@
         <v>811</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D18" s="33" t="s">
         <v>171</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>482</v>
@@ -13311,13 +13305,13 @@
         <v>812</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>171</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>486</v>
@@ -13335,13 +13329,13 @@
         <v>816</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>509</v>
@@ -13359,13 +13353,13 @@
         <v>828</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>555</v>
@@ -13383,13 +13377,13 @@
         <v>829</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>408</v>
@@ -13407,13 +13401,13 @@
         <v>832</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>571</v>
@@ -13431,13 +13425,13 @@
         <v>838</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>584</v>
@@ -13455,13 +13449,13 @@
         <v>839</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>585</v>
@@ -13479,13 +13473,13 @@
         <v>841</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D26" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>588</v>
@@ -13503,13 +13497,13 @@
         <v>845</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>441</v>
@@ -13527,13 +13521,13 @@
         <v>846</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D28" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>595</v>
@@ -13551,13 +13545,13 @@
         <v>852</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>605</v>
@@ -13575,13 +13569,13 @@
         <v>857</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D30" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>612</v>
@@ -13599,13 +13593,13 @@
         <v>864</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>622</v>
@@ -13623,13 +13617,13 @@
         <v>868</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>628</v>
@@ -13647,13 +13641,13 @@
         <v>869</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D33" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>629</v>
@@ -13671,13 +13665,13 @@
         <v>871</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>408</v>
@@ -13695,13 +13689,13 @@
         <v>881</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>648</v>
@@ -13719,13 +13713,13 @@
         <v>882</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>649</v>
@@ -13743,13 +13737,13 @@
         <v>885</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F37" s="21" t="s">
         <v>408</v>
@@ -13767,13 +13761,13 @@
         <v>891</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D38" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F38" s="21" t="s">
         <v>662</v>
@@ -13791,13 +13785,13 @@
         <v>892</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F39" s="21" t="s">
         <v>663</v>
@@ -13815,13 +13809,13 @@
         <v>893</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D40" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F40" s="21" t="s">
         <v>664</v>
@@ -13839,13 +13833,13 @@
         <v>895</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D41" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F41" s="21" t="s">
         <v>667</v>
@@ -13863,13 +13857,13 @@
         <v>898</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D42" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F42" s="21" t="s">
         <v>703</v>
@@ -13887,13 +13881,13 @@
         <v>902</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D43" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F43" s="21" t="s">
         <v>677</v>
@@ -13911,13 +13905,13 @@
         <v>863</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D44" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F44" s="21" t="s">
         <v>441</v>
@@ -13935,13 +13929,13 @@
         <v>880</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D45" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F45" s="21" t="s">
         <v>408</v>
@@ -13959,13 +13953,13 @@
         <v>767</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F46" s="21" t="s">
         <v>393</v>
@@ -13983,13 +13977,13 @@
         <v>859</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D47" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F47" s="21" t="s">
         <v>615</v>
@@ -14007,13 +14001,13 @@
         <v>754</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D48" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F48" s="21" t="s">
         <v>368</v>
@@ -14031,13 +14025,13 @@
         <v>823</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D49" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F49" s="21" t="s">
         <v>408</v>
@@ -14055,13 +14049,13 @@
         <v>825</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D50" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F50" s="21" t="s">
         <v>544</v>
@@ -14079,13 +14073,13 @@
         <v>851</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D51" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F51" s="21" t="s">
         <v>604</v>
@@ -14103,13 +14097,13 @@
         <v>875</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F52" s="21" t="s">
         <v>638</v>
@@ -14127,13 +14121,13 @@
         <v>751</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D53" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F53" s="21" t="s">
         <v>363</v>
@@ -14151,13 +14145,13 @@
         <v>735</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D54" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F54" s="21" t="s">
         <v>336</v>
@@ -14175,13 +14169,13 @@
         <v>900</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D55" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F55" s="21" t="s">
         <v>675</v>
@@ -14199,13 +14193,13 @@
         <v>763</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D56" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F56" s="21" t="s">
         <v>385</v>
@@ -14223,13 +14217,13 @@
         <v>791</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D57" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F57" s="21" t="s">
         <v>433</v>
@@ -14247,13 +14241,13 @@
         <v>742</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D58" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F58" s="21" t="s">
         <v>347</v>
@@ -14271,13 +14265,13 @@
         <v>894</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D59" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F59" s="21" t="s">
         <v>666</v>
@@ -14295,13 +14289,13 @@
         <v>861</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D60" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F60" s="21" t="s">
         <v>441</v>
@@ -14319,13 +14313,13 @@
         <v>793</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D61" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F61" s="21" t="s">
         <v>438</v>
@@ -14343,13 +14337,13 @@
         <v>821</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F62" s="21" t="s">
         <v>528</v>
@@ -14367,13 +14361,13 @@
         <v>855</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D63" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F63" s="21" t="s">
         <v>611</v>
@@ -14391,13 +14385,13 @@
         <v>877</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D64" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F64" s="21" t="s">
         <v>642</v>
@@ -14415,13 +14409,13 @@
         <v>862</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F65" s="21" t="s">
         <v>620</v>
@@ -14439,13 +14433,13 @@
         <v>712</v>
       </c>
       <c r="C66" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F66" s="21" t="s">
         <v>295</v>
@@ -14463,13 +14457,13 @@
         <v>795</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F67" s="21" t="s">
         <v>441</v>
@@ -14487,13 +14481,13 @@
         <v>814</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F68" s="21" t="s">
         <v>507</v>
@@ -14511,13 +14505,13 @@
         <v>889</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D69" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F69" s="21" t="s">
         <v>659</v>
@@ -14535,13 +14529,13 @@
         <v>867</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F70" s="21" t="s">
         <v>627</v>
@@ -14562,13 +14556,13 @@
         <v>706</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F71" s="21" t="s">
         <v>283</v>
@@ -14589,13 +14583,13 @@
         <v>804</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D72" s="33" t="s">
         <v>171</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F72" s="21" t="s">
         <v>460</v>
@@ -14613,13 +14607,13 @@
         <v>798</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D73" s="33" t="s">
         <v>171</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F73" s="21" t="s">
         <v>446</v>
@@ -14637,13 +14631,13 @@
         <v>759</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F74" s="21" t="s">
         <v>377</v>
@@ -14661,13 +14655,13 @@
         <v>700</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F75" s="21" t="s">
         <v>647</v>
@@ -14685,13 +14679,13 @@
         <v>771</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F76" s="21" t="s">
         <v>401</v>
@@ -14709,13 +14703,13 @@
         <v>844</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F77" s="21" t="s">
         <v>594</v>
@@ -14733,13 +14727,13 @@
         <v>876</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D78" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F78" s="21" t="s">
         <v>640</v>
@@ -14757,13 +14751,13 @@
         <v>778</v>
       </c>
       <c r="C79" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D79" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F79" s="21" t="s">
         <v>416</v>
@@ -14781,13 +14775,13 @@
         <v>872</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D80" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F80" s="21" t="s">
         <v>632</v>
@@ -14805,13 +14799,13 @@
         <v>822</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D81" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F81" s="21" t="s">
         <v>408</v>
@@ -14829,13 +14823,13 @@
         <v>716</v>
       </c>
       <c r="C82" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D82" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F82" s="21" t="s">
         <v>301</v>
@@ -14853,13 +14847,13 @@
         <v>888</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D83" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F83" s="21" t="s">
         <v>657</v>
@@ -14877,13 +14871,13 @@
         <v>741</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D84" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F84" s="21" t="s">
         <v>684</v>
@@ -14901,13 +14895,13 @@
         <v>813</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D85" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F85" s="21" t="s">
         <v>500</v>
@@ -14928,13 +14922,13 @@
         <v>842</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F86" s="21" t="s">
         <v>590</v>
@@ -14952,13 +14946,13 @@
         <v>727</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D87" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E87" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F87" s="21" t="s">
         <v>322</v>
@@ -14976,13 +14970,13 @@
         <v>820</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D88" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F88" s="21" t="s">
         <v>524</v>
@@ -15000,13 +14994,13 @@
         <v>737</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F89" s="21" t="s">
         <v>408</v>
@@ -15026,13 +15020,13 @@
         <v>886</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D90" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F90" s="21" t="s">
         <v>655</v>
@@ -15050,13 +15044,13 @@
         <v>830</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D91" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F91" s="21" t="s">
         <v>564</v>
@@ -15074,13 +15068,13 @@
         <v>724</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D92" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F92" s="21" t="s">
         <v>316</v>
@@ -15098,13 +15092,13 @@
         <v>901</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D93" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F93" s="21" t="s">
         <v>678</v>
@@ -15122,13 +15116,13 @@
         <v>849</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D94" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F94" s="21" t="s">
         <v>600</v>
@@ -15146,13 +15140,13 @@
         <v>708</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D95" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F95" s="21" t="s">
         <v>287</v>
@@ -15170,13 +15164,13 @@
         <v>854</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D96" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F96" s="21" t="s">
         <v>609</v>
@@ -15194,13 +15188,13 @@
         <v>765</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D97" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F97" s="21" t="s">
         <v>389</v>
@@ -15218,13 +15212,13 @@
         <v>836</v>
       </c>
       <c r="C98" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D98" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F98" s="21" t="s">
         <v>441</v>
@@ -15245,13 +15239,13 @@
         <v>874</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D99" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F99" s="21" t="s">
         <v>636</v>
@@ -15269,13 +15263,13 @@
         <v>818</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F100" s="21" t="s">
         <v>408</v>
@@ -15293,13 +15287,13 @@
         <v>711</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D101" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F101" s="21" t="s">
         <v>293</v>
@@ -15317,13 +15311,13 @@
         <v>837</v>
       </c>
       <c r="C102" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D102" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F102" s="21" t="s">
         <v>583</v>
@@ -15341,13 +15335,13 @@
         <v>688</v>
       </c>
       <c r="C103" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D103" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F103" s="21" t="s">
         <v>414</v>
@@ -15365,13 +15359,13 @@
         <v>777</v>
       </c>
       <c r="C104" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D104" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F104" s="21" t="s">
         <v>412</v>
@@ -15391,13 +15385,13 @@
         <v>858</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D105" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F105" s="21" t="s">
         <v>441</v>
@@ -15415,13 +15409,13 @@
         <v>896</v>
       </c>
       <c r="C106" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D106" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F106" s="21" t="s">
         <v>669</v>
@@ -15439,13 +15433,13 @@
         <v>903</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D107" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E107" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F107" s="21" t="s">
         <v>679</v>
@@ -15463,13 +15457,13 @@
         <v>732</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D108" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E108" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F108" s="21" t="s">
         <v>331</v>
@@ -15487,13 +15481,13 @@
         <v>776</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D109" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F109" s="21" t="s">
         <v>411</v>
@@ -15511,13 +15505,13 @@
         <v>887</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D110" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F110" s="21" t="s">
         <v>656</v>
@@ -15535,13 +15529,13 @@
         <v>721</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D111" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E111" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F111" s="21" t="s">
         <v>310</v>
@@ -15559,13 +15553,13 @@
         <v>782</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D112" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E112" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F112" s="21" t="s">
         <v>423</v>
@@ -15585,13 +15579,13 @@
         <v>709</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D113" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F113" s="21" t="s">
         <v>289</v>
@@ -15609,13 +15603,13 @@
         <v>865</v>
       </c>
       <c r="C114" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D114" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F114" s="21" t="s">
         <v>624</v>
@@ -15635,13 +15629,13 @@
         <v>755</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D115" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F115" s="21" t="s">
         <v>370</v>
@@ -15659,13 +15653,13 @@
         <v>730</v>
       </c>
       <c r="C116" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D116" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F116" s="21" t="s">
         <v>310</v>
@@ -15683,13 +15677,13 @@
         <v>847</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D117" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F117" s="21" t="s">
         <v>597</v>
@@ -15707,13 +15701,13 @@
         <v>780</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D118" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F118" s="21" t="s">
         <v>419</v>
@@ -15731,13 +15725,13 @@
         <v>899</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D119" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F119" s="21" t="s">
         <v>673</v>
@@ -15755,13 +15749,13 @@
         <v>878</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D120" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F120" s="21" t="s">
         <v>441</v>
@@ -15779,13 +15773,13 @@
         <v>720</v>
       </c>
       <c r="C121" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D121" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F121" s="21" t="s">
         <v>308</v>
@@ -15803,13 +15797,13 @@
         <v>723</v>
       </c>
       <c r="C122" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D122" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E122" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F122" s="21" t="s">
         <v>314</v>
@@ -15829,13 +15823,13 @@
         <v>744</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D123" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F123" s="21" t="s">
         <v>351</v>
@@ -15853,13 +15847,13 @@
         <v>835</v>
       </c>
       <c r="C124" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D124" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F124" s="21" t="s">
         <v>580</v>
@@ -15877,13 +15871,13 @@
         <v>740</v>
       </c>
       <c r="C125" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D125" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F125" s="21" t="s">
         <v>345</v>
@@ -15903,13 +15897,13 @@
         <v>817</v>
       </c>
       <c r="C126" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D126" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F126" s="21" t="s">
         <v>514</v>
@@ -15927,13 +15921,13 @@
         <v>743</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D127" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F127" s="21" t="s">
         <v>349</v>
@@ -15951,13 +15945,13 @@
         <v>770</v>
       </c>
       <c r="C128" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D128" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F128" s="21" t="s">
         <v>399</v>
@@ -15975,13 +15969,13 @@
         <v>884</v>
       </c>
       <c r="C129" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D129" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E129" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F129" s="21" t="s">
         <v>653</v>
@@ -15999,13 +15993,13 @@
         <v>897</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D130" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F130" s="21" t="s">
         <v>671</v>
@@ -16023,13 +16017,13 @@
         <v>826</v>
       </c>
       <c r="C131" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D131" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F131" s="21" t="s">
         <v>549</v>
@@ -16047,13 +16041,13 @@
         <v>860</v>
       </c>
       <c r="C132" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D132" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F132" s="21" t="s">
         <v>617</v>
@@ -16071,13 +16065,13 @@
         <v>710</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D133" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E133" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F133" s="21" t="s">
         <v>291</v>
@@ -16095,13 +16089,13 @@
         <v>794</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D134" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F134" s="21" t="s">
         <v>439</v>
@@ -16119,13 +16113,13 @@
         <v>840</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D135" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F135" s="21" t="s">
         <v>587</v>
@@ -16143,13 +16137,13 @@
         <v>775</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D136" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F136" s="21" t="s">
         <v>408</v>
@@ -16169,13 +16163,13 @@
         <v>824</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D137" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F137" s="21" t="s">
         <v>541</v>
@@ -16193,13 +16187,13 @@
         <v>729</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D138" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F138" s="21" t="s">
         <v>326</v>
@@ -16270,13 +16264,13 @@
         <v>747</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D139" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F139" s="21" t="s">
         <v>357</v>
@@ -16294,13 +16288,13 @@
         <v>853</v>
       </c>
       <c r="C140" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D140" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F140" s="21" t="s">
         <v>607</v>
@@ -16318,13 +16312,13 @@
         <v>805</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D141" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F141" s="21" t="s">
         <v>464</v>
@@ -16342,13 +16336,13 @@
         <v>725</v>
       </c>
       <c r="C142" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D142" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E142" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F142" s="21" t="s">
         <v>318</v>
@@ -16366,13 +16360,13 @@
         <v>802</v>
       </c>
       <c r="C143" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D143" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F143" s="21" t="s">
         <v>453</v>
@@ -16390,13 +16384,13 @@
         <v>768</v>
       </c>
       <c r="C144" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D144" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F144" s="21" t="s">
         <v>395</v>
@@ -16414,13 +16408,13 @@
         <v>753</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D145" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E145" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F145" s="21" t="s">
         <v>366</v>
@@ -16438,13 +16432,13 @@
         <v>788</v>
       </c>
       <c r="C146" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D146" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E146" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F146" s="21" t="s">
         <v>430</v>
@@ -16462,13 +16456,13 @@
         <v>773</v>
       </c>
       <c r="C147" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D147" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E147" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F147" s="21" t="s">
         <v>686</v>
@@ -16487,13 +16481,13 @@
         <v>786</v>
       </c>
       <c r="C148" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D148" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E148" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F148" s="21" t="s">
         <v>427</v>
@@ -16511,13 +16505,13 @@
         <v>726</v>
       </c>
       <c r="C149" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D149" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E149" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F149" s="21" t="s">
         <v>320</v>
@@ -16535,13 +16529,13 @@
         <v>745</v>
       </c>
       <c r="C150" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D150" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F150" s="21" t="s">
         <v>353</v>
@@ -16559,13 +16553,13 @@
         <v>815</v>
       </c>
       <c r="C151" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D151" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E151" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F151" s="21" t="s">
         <v>506</v>
@@ -16583,13 +16577,13 @@
         <v>850</v>
       </c>
       <c r="C152" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D152" s="28" t="s">
         <v>169</v>
       </c>
       <c r="E152" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F152" s="21" t="s">
         <v>602</v>
@@ -16607,13 +16601,13 @@
         <v>691</v>
       </c>
       <c r="C153" s="29" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D153" s="30" t="s">
         <v>914</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F153" s="21" t="s">
         <v>435</v>
@@ -16631,13 +16625,13 @@
         <v>772</v>
       </c>
       <c r="C154" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D154" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E154" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F154" s="21" t="s">
         <v>403</v>
@@ -16655,13 +16649,13 @@
         <v>810</v>
       </c>
       <c r="C155" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D155" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F155" s="21" t="s">
         <v>480</v>
@@ -16679,13 +16673,13 @@
         <v>796</v>
       </c>
       <c r="C156" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D156" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E156" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F156" s="21" t="s">
         <v>408</v>
@@ -16705,13 +16699,13 @@
         <v>843</v>
       </c>
       <c r="C157" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D157" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E157" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F157" s="21" t="s">
         <v>592</v>
@@ -16731,13 +16725,13 @@
         <v>819</v>
       </c>
       <c r="C158" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D158" s="33" t="s">
         <v>171</v>
       </c>
       <c r="E158" s="33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F158" s="21" t="s">
         <v>408</v>
@@ -16755,13 +16749,13 @@
         <v>870</v>
       </c>
       <c r="C159" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D159" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E159" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F159" s="21" t="s">
         <v>408</v>
@@ -16779,13 +16773,13 @@
         <v>731</v>
       </c>
       <c r="C160" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D160" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F160" s="21" t="s">
         <v>329</v>
@@ -16803,13 +16797,13 @@
         <v>769</v>
       </c>
       <c r="C161" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D161" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F161" s="21" t="s">
         <v>397</v>
@@ -16827,13 +16821,13 @@
         <v>718</v>
       </c>
       <c r="C162" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D162" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E162" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F162" s="21" t="s">
         <v>304</v>
@@ -16851,13 +16845,13 @@
         <v>785</v>
       </c>
       <c r="C163" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D163" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F163" s="21" t="s">
         <v>425</v>
@@ -16876,13 +16870,13 @@
         <v>873</v>
       </c>
       <c r="C164" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D164" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E164" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F164" s="21" t="s">
         <v>634</v>
@@ -16900,13 +16894,13 @@
         <v>762</v>
       </c>
       <c r="C165" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D165" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E165" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F165" s="21" t="s">
         <v>384</v>
@@ -16924,13 +16918,13 @@
         <v>866</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D166" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E166" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F166" s="21" t="s">
         <v>626</v>
@@ -16948,13 +16942,13 @@
         <v>774</v>
       </c>
       <c r="C167" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D167" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E167" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F167" s="21" t="s">
         <v>406</v>
@@ -16972,13 +16966,13 @@
         <v>801</v>
       </c>
       <c r="C168" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D168" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E168" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F168" s="21" t="s">
         <v>451</v>
@@ -16996,13 +16990,13 @@
         <v>707</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D169" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E169" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F169" s="21" t="s">
         <v>285</v>
@@ -17020,13 +17014,13 @@
         <v>848</v>
       </c>
       <c r="C170" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D170" s="28" t="s">
         <v>173</v>
       </c>
       <c r="E170" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F170" s="21" t="s">
         <v>696</v>
@@ -17044,13 +17038,13 @@
         <v>799</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D171" s="28" t="s">
         <v>168</v>
       </c>
       <c r="E171" s="28" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F171" s="21" t="s">
         <v>448</v>
@@ -17068,13 +17062,13 @@
         <v>736</v>
       </c>
       <c r="C172" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D172" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E172" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F172" s="21" t="s">
         <v>338</v>
@@ -17092,13 +17086,13 @@
         <v>758</v>
       </c>
       <c r="C173" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D173" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E173" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F173" s="21" t="s">
         <v>376</v>
@@ -17116,13 +17110,13 @@
         <v>808</v>
       </c>
       <c r="C174" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E174" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F174" s="21" t="s">
         <v>535</v>
@@ -17140,13 +17134,13 @@
         <v>728</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D175" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E175" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F175" s="21" t="s">
         <v>324</v>
@@ -17164,13 +17158,13 @@
         <v>809</v>
       </c>
       <c r="C176" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D176" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E176" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F176" s="21" t="s">
         <v>476</v>
@@ -17188,13 +17182,13 @@
         <v>748</v>
       </c>
       <c r="C177" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D177" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E177" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F177" s="21" t="s">
         <v>359</v>
@@ -17212,13 +17206,13 @@
         <v>738</v>
       </c>
       <c r="C178" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D178" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E178" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F178" s="21" t="s">
         <v>341</v>
@@ -17236,13 +17230,13 @@
         <v>760</v>
       </c>
       <c r="C179" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D179" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E179" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F179" s="21" t="s">
         <v>379</v>
@@ -17261,13 +17255,13 @@
         <v>890</v>
       </c>
       <c r="C180" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D180" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E180" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F180" s="21" t="s">
         <v>661</v>
@@ -17285,13 +17279,13 @@
         <v>879</v>
       </c>
       <c r="C181" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D181" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E181" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F181" s="21" t="s">
         <v>644</v>
@@ -17309,13 +17303,13 @@
         <v>833</v>
       </c>
       <c r="C182" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D182" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E182" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F182" s="21" t="s">
         <v>574</v>
@@ -17333,13 +17327,13 @@
         <v>719</v>
       </c>
       <c r="C183" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D183" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E183" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F183" s="21" t="s">
         <v>306</v>
@@ -17357,13 +17351,13 @@
         <v>757</v>
       </c>
       <c r="C184" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D184" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F184" s="21" t="s">
         <v>374</v>
@@ -17381,13 +17375,13 @@
         <v>827</v>
       </c>
       <c r="C185" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D185" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E185" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F185" s="21" t="s">
         <v>553</v>
@@ -17405,13 +17399,13 @@
         <v>739</v>
       </c>
       <c r="C186" s="37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D186" s="38" t="s">
         <v>912</v>
       </c>
       <c r="E186" s="39" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F186" s="21" t="s">
         <v>343</v>
@@ -17429,13 +17423,13 @@
         <v>717</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D187" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E187" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F187" s="21" t="s">
         <v>302</v>
@@ -17453,13 +17447,13 @@
         <v>715</v>
       </c>
       <c r="C188" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D188" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E188" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F188" s="21" t="s">
         <v>299</v>
@@ -17477,13 +17471,13 @@
         <v>834</v>
       </c>
       <c r="C189" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D189" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E189" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F189" s="21" t="s">
         <v>577</v>
@@ -17501,13 +17495,13 @@
         <v>856</v>
       </c>
       <c r="C190" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D190" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E190" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F190" s="21" t="s">
         <v>441</v>
@@ -17525,13 +17519,13 @@
         <v>761</v>
       </c>
       <c r="C191" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D191" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E191" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F191" s="21" t="s">
         <v>381</v>
@@ -17549,13 +17543,13 @@
         <v>766</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D192" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E192" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F192" s="21" t="s">
         <v>391</v>
@@ -17573,13 +17567,13 @@
         <v>756</v>
       </c>
       <c r="C193" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D193" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E193" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F193" s="21" t="s">
         <v>372</v>
@@ -17597,13 +17591,13 @@
         <v>797</v>
       </c>
       <c r="C194" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D194" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E194" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F194" s="21" t="s">
         <v>444</v>
@@ -17621,13 +17615,13 @@
         <v>781</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D195" s="28" t="s">
         <v>910</v>
       </c>
       <c r="E195" s="28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F195" s="21" t="s">
         <v>421</v>
@@ -17645,13 +17639,13 @@
         <v>746</v>
       </c>
       <c r="C196" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D196" s="28" t="s">
         <v>906</v>
       </c>
       <c r="E196" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F196" s="21" t="s">
         <v>355</v>
@@ -17669,13 +17663,13 @@
         <v>722</v>
       </c>
       <c r="C197" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D197" s="33" t="s">
         <v>913</v>
       </c>
       <c r="E197" s="33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F197" s="21" t="s">
         <v>312</v>
@@ -17693,13 +17687,13 @@
         <v>831</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D198" s="35" t="s">
         <v>907</v>
       </c>
       <c r="E198" s="35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F198" s="21" t="s">
         <v>568</v>
@@ -17717,13 +17711,13 @@
         <v>764</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D199" s="28" t="s">
         <v>911</v>
       </c>
       <c r="E199" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F199" s="21" t="s">
         <v>387</v>
@@ -17741,13 +17735,13 @@
         <v>883</v>
       </c>
       <c r="C200" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D200" s="33" t="s">
         <v>908</v>
       </c>
       <c r="E200" s="33" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F200" s="21" t="s">
         <v>651</v>
@@ -17765,13 +17759,13 @@
         <v>734</v>
       </c>
       <c r="C201" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D201" s="28" t="s">
         <v>905</v>
       </c>
       <c r="E201" s="28" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F201" s="21" t="s">
         <v>334</v>
@@ -17789,13 +17783,13 @@
         <v>800</v>
       </c>
       <c r="C202" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D202" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E202" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F202" s="21" t="s">
         <v>693</v>
@@ -17813,13 +17807,13 @@
         <v>714</v>
       </c>
       <c r="C203" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D203" s="28" t="s">
         <v>909</v>
       </c>
       <c r="E203" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F203" s="21" t="s">
         <v>298</v>
@@ -17835,35 +17829,13 @@
       <c r="I204" s="17"/>
       <c r="J204" s="17"/>
     </row>
-    <row r="205" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="42"/>
-      <c r="B205" s="43"/>
-    </row>
     <row r="206" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="42"/>
-      <c r="B206" s="44"/>
-    </row>
-    <row r="207" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="42"/>
-      <c r="B207" s="43"/>
+      <c r="B206" s="41"/>
     </row>
     <row r="208" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="42"/>
-      <c r="B208" s="45"/>
-    </row>
-    <row r="209" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="42"/>
-      <c r="B209" s="43"/>
-    </row>
-    <row r="210" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="42"/>
-      <c r="B210" s="43"/>
-    </row>
-    <row r="211" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="42"/>
-      <c r="B211" s="43"/>
-    </row>
-    <row r="213" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B208" s="42"/>
+    </row>
+    <row r="213" spans="6:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F213" s="20"/>
     </row>
     <row r="225" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -17880,10 +17852,10 @@
       <c r="K234"/>
     </row>
     <row r="236" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="41"/>
+      <c r="A236" s="43"/>
     </row>
     <row r="237" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="41"/>
+      <c r="A237" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F203" xr:uid="{4A81ECA9-B44D-4397-8AB5-501544011731}">
